--- a/perturbations/J1/equipe-29-product-backlog-v1.1.xlsx
+++ b/perturbations/J1/equipe-29-product-backlog-v1.1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxence\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxence\Documents\IPSSI\4e\Apocalipssi\perturbations\J1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF70C01-0393-47A9-AEB6-5EDD2EE55452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C173457B-8BC3-4E7E-B812-E5408CB77C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-825" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-825" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="208">
   <si>
     <t>A</t>
   </si>
@@ -668,13 +668,19 @@
   </si>
   <si>
     <t>En revue PO</t>
+  </si>
+  <si>
+    <t>Suivre sa classe</t>
+  </si>
+  <si>
+    <t>US-24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -823,6 +829,21 @@
       <color rgb="FF1E1B4B"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1E1B4B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -916,7 +937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -974,6 +995,10 @@
     <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1564,7 +1589,7 @@
         <v>191</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>45</v>
+        <v>206</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>50</v>
@@ -1580,7 +1605,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8" customWidth="1"/>
@@ -1916,7 +1941,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>100</v>
       </c>
@@ -1951,7 +1976,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>103</v>
       </c>
@@ -1986,7 +2011,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>106</v>
       </c>
@@ -2021,7 +2046,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>110</v>
       </c>
@@ -2056,7 +2081,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>113</v>
       </c>
@@ -2090,8 +2115,9 @@
       <c r="K21" s="20" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L21" s="34"/>
+    </row>
+    <row r="22" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>192</v>
       </c>
@@ -2126,7 +2152,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>194</v>
       </c>
@@ -2161,7 +2187,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>118</v>
       </c>
@@ -2196,7 +2222,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>122</v>
       </c>
@@ -2231,7 +2257,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>125</v>
       </c>
@@ -2266,7 +2292,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>129</v>
       </c>
@@ -2301,7 +2327,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>132</v>
       </c>
@@ -2336,7 +2362,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>195</v>
       </c>
@@ -2371,7 +2397,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>135</v>
       </c>
@@ -2406,7 +2432,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>141</v>
       </c>
@@ -2441,7 +2467,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>144</v>
       </c>
@@ -2477,8 +2503,8 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>195</v>
+      <c r="A33" s="35" t="s">
+        <v>207</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>190</v>
@@ -2533,6 +2559,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
